--- a/tests/pivot-slicer-showcase.xlsx
+++ b/tests/pivot-slicer-showcase.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xy/Documents/Nexolyra/demo-user-space/office/"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1AEF291-1EC5-074A-9937-43EBAC8352DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
